--- a/剧情文件及美术补充/静语纹_四章剧情_无旁白版_v2.xlsx
+++ b/剧情文件及美术补充/静语纹_四章剧情_无旁白版_v2.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\she-nicest-weave-the-truth\剧情文件及美术补充\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21094" windowHeight="8434"/>
+    <workbookView windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="剧情对白" sheetId="1" r:id="rId1"/>
@@ -27,9 +32,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="139">
-  <si>
-    <r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="135">
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>1.</t>
     </r>
     <r>
@@ -177,6 +187,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>可我听说，真正让那些机器运转的是学院写的</t>
     </r>
     <r>
@@ -217,6 +232,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>学院写他们的符号，我们照规矩把纹样织出来。至于什么算</t>
     </r>
     <r>
@@ -260,6 +280,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>莉娅</t>
     </r>
     <r>
@@ -284,6 +309,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>亚瑟</t>
     </r>
     <r>
@@ -308,6 +338,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>诺拉</t>
     </r>
     <r>
@@ -343,15 +378,6 @@
     <t>对。记住，静语丝不是越多越好，关系对了才算纹样。</t>
   </si>
   <si>
-    <t>哪一步没看明白，也可以问小织。墙边那个小家伙是工坊新进的小型机器人助手，基础织法和机器怎么用，它都能提醒你。</t>
-  </si>
-  <si>
-    <t>机器人也能教人织静语纹？</t>
-  </si>
-  <si>
-    <t>教你上路而已。别太依赖它——等纹样越来越复杂，现成的提醒就不够用了。真碰上没见过的问题，最后还是得靠你自己想。</t>
-  </si>
-  <si>
     <t>苦恼</t>
   </si>
   <si>
@@ -404,6 +430,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>我们有</t>
     </r>
     <r>
@@ -473,6 +504,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>把字符换成颜色，把“为真”换成“纹样”……这不就是</t>
     </r>
     <r>
@@ -500,6 +536,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>如果</t>
     </r>
     <r>
@@ -588,6 +629,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>今天学</t>
     </r>
     <r>
@@ -640,6 +686,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>如果用学院的写法</t>
     </r>
     <r>
@@ -741,6 +792,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>假设</t>
     </r>
     <r>
@@ -820,6 +876,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>三号静语丝受潮后的</t>
     </r>
     <r>
@@ -884,6 +945,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>正好。诺拉，今天学</t>
     </r>
     <r>
@@ -924,6 +990,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <charset val="134"/>
+      </rPr>
       <t>A</t>
     </r>
     <r>
@@ -1128,6 +1199,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>连着下了几天雨以后就不对劲了。邮报机把一封信判给两条路，清扫机来回改向，连门禁都能同时亮</t>
     </r>
     <r>
@@ -1197,9 +1273,6 @@
   </si>
   <si>
     <t>它不是选错了一条路……它像是同时认出了两条互相冲突的状态。</t>
-  </si>
-  <si>
-    <t>小织也是，前几天被人不小心放在窗台旁淋了雨，现在连句完整的话都说不出来，机械厂来的维修工却说他们也找不到问题……</t>
   </si>
   <si>
     <t>请远离那台机器。学院已经收到异常报告。初步判断是部分工坊纹样偏离程式。</t>
@@ -1805,7 +1878,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2451,8 +2524,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G105"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.1" outlineLevelCol="6"/>
+  <dimension ref="A1:G101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -2460,7 +2533,7 @@
     <col min="7" max="7" width="68" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.15" spans="1:7">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2777,7 +2850,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" ht="22" customHeight="1" spans="1:7">
+    <row r="18" ht="25" customHeight="1" spans="1:7">
       <c r="A18" s="4" t="s">
         <v>30</v>
       </c>
@@ -2788,12 +2861,14 @@
       <c r="D18" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="4"/>
+      <c r="E18" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:7">
@@ -2809,114 +2884,110 @@
       <c r="D19" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="F19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:7">
       <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="4"/>
+      <c r="C20" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="D20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C23" s="4"/>
       <c r="D23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C24" s="4"/>
       <c r="D24" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
@@ -2928,20 +2999,18 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C25" s="4"/>
       <c r="D25" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>45</v>
@@ -2949,213 +3018,213 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="D26" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E26" s="4"/>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
+      <c r="F26" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="4"/>
+        <v>9</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D27" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D28" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:7">
       <c r="A29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="C29" s="6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>50</v>
+      <c r="G29" s="7" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:7">
       <c r="A30" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>9</v>
-      </c>
       <c r="C30" s="6" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>51</v>
+      <c r="G30" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:7">
       <c r="A31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:7">
       <c r="A32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>13</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C33" s="4"/>
       <c r="D33" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:7">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="B34" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="4"/>
       <c r="D34" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>57</v>
+        <v>10</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:7">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C35" s="4"/>
       <c r="D35" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:7">
-      <c r="A36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="4" t="s">
+      <c r="A36" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="4"/>
@@ -3164,7 +3233,7 @@
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>60</v>
@@ -3172,9 +3241,9 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:7">
       <c r="A37" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="4"/>
@@ -3191,9 +3260,9 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:7">
       <c r="A38" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="4"/>
@@ -3209,10 +3278,10 @@
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:7">
-      <c r="A39" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="6" t="s">
+      <c r="A39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="4"/>
@@ -3229,9 +3298,9 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:7">
       <c r="A40" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="4"/>
@@ -3240,17 +3309,17 @@
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G40" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:7">
-      <c r="A41" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="6" t="s">
+      <c r="A41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="4"/>
@@ -3261,18 +3330,20 @@
       <c r="F41" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G41" s="7" t="s">
+      <c r="G41" s="5" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="4"/>
+      <c r="C42" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D42" s="6" t="s">
         <v>24</v>
       </c>
@@ -3280,95 +3351,93 @@
       <c r="F42" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G42" s="7" t="s">
+      <c r="G42" s="5" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:7">
-      <c r="A43" s="8" t="s">
-        <v>59</v>
+      <c r="A43" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="4"/>
+      <c r="C43" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D43" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="4"/>
+      <c r="E43" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E44" s="4"/>
-      <c r="F44" s="4" t="s">
-        <v>10</v>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:7">
       <c r="A45" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="C45" s="4"/>
       <c r="D45" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E45" s="4"/>
-      <c r="F45" s="4" t="s">
-        <v>14</v>
+      <c r="F45" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:7">
       <c r="A46" s="4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="C46" s="4"/>
       <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E46" s="4"/>
       <c r="F46" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:7">
       <c r="A47" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>9</v>
@@ -3378,8 +3447,8 @@
         <v>26</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="F47" s="6" t="s">
-        <v>26</v>
+      <c r="F47" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>72</v>
@@ -3387,7 +3456,7 @@
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:7">
       <c r="A48" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>9</v>
@@ -3397,8 +3466,8 @@
         <v>26</v>
       </c>
       <c r="E48" s="4"/>
-      <c r="F48" s="6" t="s">
-        <v>28</v>
+      <c r="F48" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>73</v>
@@ -3406,18 +3475,20 @@
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:7">
       <c r="A49" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C49" s="4"/>
+      <c r="C49" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D49" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E49" s="4"/>
       <c r="F49" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>74</v>
@@ -3425,18 +3496,20 @@
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:7">
       <c r="A50" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C50" s="4"/>
+      <c r="C50" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="E50" s="4"/>
       <c r="F50" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>75</v>
@@ -3444,102 +3517,110 @@
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:7">
       <c r="A51" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C51" s="4"/>
+      <c r="C51" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="D51" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E51" s="4"/>
       <c r="F51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>76</v>
+        <v>14</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:7">
       <c r="A52" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E52" s="4"/>
       <c r="F52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:7">
       <c r="A53" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>78</v>
+        <v>24</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:7">
       <c r="A54" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E54" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F54" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="7" t="s">
+      <c r="G54" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:7">
       <c r="A55" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E55" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F55" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G55" s="5" t="s">
         <v>81</v>
@@ -3547,42 +3628,42 @@
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:7">
       <c r="A56" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:7">
       <c r="A57" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>14</v>
@@ -3593,19 +3674,19 @@
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:7">
       <c r="A58" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>10</v>
@@ -3616,116 +3697,104 @@
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:7">
       <c r="A59" s="4" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E59" s="4"/>
       <c r="F59" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:7">
       <c r="A60" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C60" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="C60" s="4"/>
       <c r="D60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>86</v>
+        <v>26</v>
+      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:7">
       <c r="A61" s="4" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="C61" s="4"/>
       <c r="D61" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="E61" s="4"/>
       <c r="F61" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>87</v>
+      <c r="G61" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:7">
       <c r="A62" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C62" s="4"/>
       <c r="D62" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>89</v>
+        <v>10</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:7">
       <c r="A63" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E63" s="4"/>
-      <c r="F63" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G63" s="7" t="s">
+      <c r="F63" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:7">
       <c r="A64" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>9</v>
@@ -3734,17 +3803,19 @@
       <c r="D64" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E64" s="4"/>
+      <c r="E64" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="F64" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G64" s="7" t="s">
+      <c r="G64" s="5" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:7">
       <c r="A65" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>9</v>
@@ -3753,7 +3824,9 @@
       <c r="D65" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E65" s="4"/>
+      <c r="E65" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F65" s="4" t="s">
         <v>10</v>
       </c>
@@ -3763,26 +3836,26 @@
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:7">
       <c r="A66" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E66" s="4"/>
-      <c r="F66" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="5" t="s">
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:7">
       <c r="A67" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>9</v>
@@ -3792,7 +3865,7 @@
         <v>24</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>10</v>
@@ -3803,134 +3876,136 @@
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:7">
       <c r="A68" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="E68" s="4"/>
       <c r="F68" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:7">
       <c r="A69" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="D69" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E69" s="4"/>
       <c r="F69" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>97</v>
+        <v>28</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:7">
       <c r="A70" s="4" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="D70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:7">
       <c r="A71" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E71" s="4"/>
       <c r="F71" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="G71" s="5" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:7">
       <c r="A72" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E72" s="4"/>
-      <c r="F72" s="6" t="s">
-        <v>28</v>
+      <c r="F72" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G72" s="5" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:7">
-      <c r="A73" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>42</v>
+      <c r="A73" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E73" s="4"/>
-      <c r="F73" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G73" s="7" t="s">
+      <c r="F73" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" ht="25" customHeight="1" spans="1:7">
+      <c r="A74" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="74" ht="22" customHeight="1" spans="1:7">
-      <c r="A74" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="B74" s="4" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>20</v>
@@ -3939,40 +4014,42 @@
         <v>26</v>
       </c>
       <c r="E74" s="4"/>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>103</v>
+      <c r="F74" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:7">
       <c r="A75" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:7">
       <c r="A76" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>20</v>
@@ -3981,16 +4058,16 @@
         <v>26</v>
       </c>
       <c r="E76" s="4"/>
-      <c r="F76" s="4" t="s">
-        <v>22</v>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:7">
       <c r="A77" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>9</v>
@@ -3998,20 +4075,22 @@
       <c r="C77" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" s="4"/>
+      <c r="D77" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="F77" s="4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="78" ht="25" customHeight="1" spans="1:7">
+    <row r="78" ht="22" customHeight="1" spans="1:7">
       <c r="A78" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>9</v>
@@ -4024,15 +4103,15 @@
       </c>
       <c r="E78" s="4"/>
       <c r="F78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G78" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="5" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:7">
       <c r="A79" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>9</v>
@@ -4041,13 +4120,11 @@
         <v>20</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>109</v>
@@ -4055,7 +4132,7 @@
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:7">
       <c r="A80" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>9</v>
@@ -4067,8 +4144,8 @@
         <v>26</v>
       </c>
       <c r="E80" s="4"/>
-      <c r="F80" s="6" t="s">
-        <v>26</v>
+      <c r="F80" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="G80" s="5" t="s">
         <v>110</v>
@@ -4076,33 +4153,31 @@
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:7">
       <c r="A81" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="D81" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="4"/>
       <c r="F81" s="4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:7">
       <c r="A82" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>20</v>
@@ -4112,18 +4187,18 @@
       </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:7">
       <c r="A83" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>20</v>
@@ -4133,18 +4208,18 @@
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:7">
       <c r="A84" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>20</v>
@@ -4157,15 +4232,15 @@
         <v>22</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:7">
       <c r="A85" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>20</v>
@@ -4175,7 +4250,7 @@
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G85" s="5" t="s">
         <v>116</v>
@@ -4183,182 +4258,174 @@
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:7">
       <c r="A86" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E86" s="4"/>
       <c r="F86" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:7">
       <c r="A87" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:7">
       <c r="A88" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="4" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:7">
       <c r="A89" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>42</v>
+        <v>117</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:7">
       <c r="A90" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C90" s="4"/>
       <c r="D90" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:7">
       <c r="A91" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:7">
       <c r="A92" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4" t="s">
-        <v>14</v>
+        <v>24</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:7">
       <c r="A93" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E93" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="F93" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:7">
       <c r="A94" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="4"/>
       <c r="D94" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E94" s="4"/>
       <c r="F94" s="4" t="s">
@@ -4370,7 +4437,7 @@
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:7">
       <c r="A95" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>9</v>
@@ -4379,8 +4446,8 @@
         <v>26</v>
       </c>
       <c r="E95" s="4"/>
-      <c r="F95" s="4" t="s">
-        <v>22</v>
+      <c r="F95" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="G95" s="5" t="s">
         <v>128</v>
@@ -4388,19 +4455,17 @@
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:7">
       <c r="A96" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B96" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="G96" s="5" t="s">
         <v>129</v>
@@ -4408,27 +4473,25 @@
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:7">
       <c r="A97" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B97" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>20</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E97" s="4"/>
       <c r="F97" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G97" s="7" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:7">
       <c r="A98" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B98" s="4" t="s">
         <v>9</v>
@@ -4437,8 +4500,8 @@
         <v>24</v>
       </c>
       <c r="E98" s="4"/>
-      <c r="F98" s="4" t="s">
-        <v>14</v>
+      <c r="F98" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="G98" s="5" t="s">
         <v>131</v>
@@ -4446,7 +4509,7 @@
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:7">
       <c r="A99" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B99" s="4" t="s">
         <v>9</v>
@@ -4464,109 +4527,37 @@
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:7">
       <c r="A100" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>9</v>
+        <v>122</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="101" ht="22" customHeight="1" spans="1:7">
-      <c r="A101" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G101" s="7" t="s">
+    <row r="101" spans="1:7">
+      <c r="A101" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" t="s">
+        <v>49</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+      <c r="G101" t="s">
         <v>134</v>
-      </c>
-    </row>
-    <row r="102" ht="22" customHeight="1" spans="1:7">
-      <c r="A102" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B102" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E102" s="4"/>
-      <c r="F102" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="103" ht="22" customHeight="1" spans="1:7">
-      <c r="A103" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E103" s="4"/>
-      <c r="F103" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1" spans="1:7">
-      <c r="A104" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
-      <c r="A105" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B105" t="s">
-        <v>52</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F105" t="s">
-        <v>14</v>
-      </c>
-      <c r="G105" t="s">
-        <v>138</v>
       </c>
     </row>
   </sheetData>
